--- a/output/pdf_financials_xlsx/TCW.xlsx
+++ b/output/pdf_financials_xlsx/TCW.xlsx
@@ -1348,7 +1348,7 @@
         <v>210.347</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-75.002</v>
@@ -1363,7 +1363,7 @@
         <v>-103.954</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>50.32</v>
+        <v>19.33</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-254.665</v>
@@ -1652,7 +1652,7 @@
         <v>151.617</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-46.699</v>
@@ -1667,7 +1667,7 @@
         <v>-29.328</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>15.495</v>
+        <v>-15.495</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-232.657</v>
@@ -1847,7 +1847,7 @@
         <v>151.617</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-46.699</v>
@@ -1862,7 +1862,7 @@
         <v>-29.328</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.495</v>
+        <v>-15.495</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-232.657</v>
@@ -2137,7 +2137,7 @@
         <v>210.347</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>55.551</v>
+        <v>-51.127</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-73.254</v>
@@ -2152,7 +2152,7 @@
         <v>-100.835</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>51.542</v>
+        <v>20.552</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-254.665</v>
@@ -2267,7 +2267,7 @@
         <v>321.142</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>208.388</v>
+        <v>101.71</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>149.149</v>
@@ -2282,7 +2282,7 @@
         <v>-30.396</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>153.539</v>
+        <v>122.549</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-138.064</v>
@@ -2332,7 +2332,7 @@
         <v>21.72383959066302</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.414836902502936</v>
+        <v>4.595192915876027</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>7.050388754849982</v>
@@ -2347,7 +2347,7 @@
         <v>-9.347467087358039</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.51113223616858</v>
+        <v>13.17855883137329</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-15.97072003812688</v>
@@ -2397,7 +2397,7 @@
         <v>27.92053131254546</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-37.73632703127917</v>
@@ -2412,7 +2412,7 @@
         <v>-60.82017046001116</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>69.2070747217806</v>
+        <v>180.1603724780134</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-8.641941373961872</v>
@@ -2462,7 +2462,7 @@
         <v>10.25622119566284</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.409821993313454</v>
+        <v>-2.409821993313454</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>-2.207497901177609</v>
@@ -2477,7 +2477,7 @@
         <v>-9.019032594355723</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.666286702397646</v>
+        <v>-1.666286702397646</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>-26.91287962039696</v>
@@ -6267,7 +6267,7 @@
         <v>151.617</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-46.699</v>
@@ -6282,7 +6282,7 @@
         <v>-29.328</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>15.495</v>
+        <v>-15.495</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-232.657</v>
@@ -57876,7 +57876,7 @@
         <v>-29.328</v>
       </c>
       <c r="M524" s="5" t="n">
-        <v>15.495</v>
+        <v>-15.495</v>
       </c>
       <c r="N524" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>-29.328</v>
       </c>
       <c r="M532" s="5" t="n">
-        <v>15.495</v>
+        <v>-15.495</v>
       </c>
       <c r="N532" t="inlineStr">
         <is>
@@ -64567,7 +64567,7 @@
         </is>
       </c>
       <c r="H595" s="5" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="I595" s="5" t="n">
         <v>-46.699</v>
@@ -65139,7 +65139,7 @@
         </is>
       </c>
       <c r="H601" s="5" t="n">
-        <v>53.339</v>
+        <v>-53.339</v>
       </c>
       <c r="I601" s="5" t="n">
         <v>-46.699</v>

--- a/output/pdf_financials_xlsx/TCW.xlsx
+++ b/output/pdf_financials_xlsx/TCW.xlsx
@@ -2888,16 +2888,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>127.793</v>
+        <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>175.441</v>
+        <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>181.127</v>
+        <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>210.62</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
@@ -2943,16 +2943,16 @@
         <v>146.374</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>255.586</v>
+        <v>127.793</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>350.882</v>
+        <v>175.441</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>362.254</v>
+        <v>181.127</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>421.24</v>
+        <v>210.62</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>260.678</v>
@@ -3328,16 +3328,16 @@
         <v>49.574</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>4.995</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0</v>
+        <v>5.022</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0</v>
+        <v>6.202</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0</v>
+        <v>6.269</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>12.516</v>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCW.xlsx
+++ b/output/pdf_financials_xlsx/TCW.xlsx
@@ -1171,10 +1171,10 @@
         <v>-0</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.12</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.69</v>
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>20.552</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-254.665</v>
+        <v>-239.545</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-99.827</v>
+        <v>-95.137</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
         <v>122.549</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-138.064</v>
+        <v>-122.944</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>18.569</v>
+        <v>23.259</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         <v>13.17855883137329</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-15.97072003812688</v>
+        <v>-14.22169576694483</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>2.919328188205405</v>
+        <v>3.656667258843745</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -7103,19 +7103,19 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2.423</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -49580,7 +49580,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E437" s="5" t="n">
         <v>0.029</v>
       </c>
@@ -53638,7 +53642,11 @@
           <t>Net finance cost (note 21)</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
